--- a/dados/territorio.xlsx
+++ b/dados/territorio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.sa\Documents\dashboard-oportunidades\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63C39F7-5F40-4DB6-9092-7F60DF7DB1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D703A20C-8B47-4011-9CC2-D505106F0668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3514,7 +3514,7 @@
   <autoFilter ref="A1:O592" xr:uid="{F1FEB497-9701-4180-9E5F-E582B822EF71}">
     <filterColumn colId="7">
       <filters>
-        <filter val="RAFAEL ASSMANN CAETANO"/>
+        <filter val="NATALIA FATIMA MORAES"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -12133,7 +12133,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>2201101</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>2201309</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>2201903</v>
       </c>
@@ -12274,7 +12274,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>2202901</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>2203008</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>2203206</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>2204402</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>2205524</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>2206605</v>
       </c>
@@ -12556,7 +12556,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>2206654</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>2207603</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>2208700</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>2208858</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>2209757</v>
       </c>
@@ -12791,7 +12791,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>2210623</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
         <v>3103603</v>
       </c>
@@ -19559,7 +19559,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
         <v>3104403</v>
       </c>
@@ -19606,7 +19606,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>3104601</v>
       </c>
@@ -19653,7 +19653,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
         <v>3106101</v>
       </c>
@@ -19700,7 +19700,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>3106903</v>
       </c>
@@ -19747,7 +19747,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
         <v>3107208</v>
       </c>
@@ -19794,7 +19794,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>3107505</v>
       </c>
@@ -19841,7 +19841,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
         <v>3115904</v>
       </c>
@@ -19888,7 +19888,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>3116209</v>
       </c>
@@ -19935,7 +19935,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
         <v>3119609</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>3121308</v>
       </c>
@@ -20029,7 +20029,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
         <v>3122900</v>
       </c>
@@ -20076,7 +20076,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>3125002</v>
       </c>
@@ -20123,7 +20123,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
         <v>3127388</v>
       </c>
@@ -20170,7 +20170,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>3128402</v>
       </c>
@@ -20217,7 +20217,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
         <v>3128501</v>
       </c>
@@ -20264,7 +20264,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>3132602</v>
       </c>
@@ -20311,7 +20311,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
         <v>3133006</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>3136702</v>
       </c>
@@ -20405,7 +20405,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
         <v>3138500</v>
       </c>
@@ -20452,7 +20452,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>3138609</v>
       </c>
@@ -20499,7 +20499,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
         <v>3139805</v>
       </c>
@@ -20546,7 +20546,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>3140209</v>
       </c>
@@ -20593,7 +20593,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>3140803</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>3145406</v>
       </c>
@@ -20687,7 +20687,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>3147808</v>
       </c>
@@ -20734,7 +20734,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>3149408</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
         <v>3149507</v>
       </c>
@@ -20828,7 +20828,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>3150109</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
         <v>3155405</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>3155900</v>
       </c>
@@ -20969,7 +20969,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
         <v>3156205</v>
       </c>
@@ -21016,7 +21016,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>3157278</v>
       </c>
@@ -21063,7 +21063,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
         <v>3159308</v>
       </c>
@@ -21110,7 +21110,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
         <v>3158607</v>
       </c>
@@ -21157,7 +21157,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
         <v>3160009</v>
       </c>
@@ -21204,7 +21204,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
         <v>3162906</v>
       </c>
@@ -21251,7 +21251,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
         <v>3165602</v>
       </c>
@@ -21298,7 +21298,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
         <v>3167509</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A374" s="4">
         <v>3167905</v>
       </c>
@@ -31647,26 +31647,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B96036E30F13644F923D207E371C305D" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d197ceb99055fd1a93a3a14aec1bdd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f76aa77c-8923-4724-9a6d-d588cc513697" xmlns:ns3="89c54d5b-05ac-45d5-9242-aabb385cc5ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b86266bfd619f312673123d0bd20d23" ns2:_="" ns3:_="">
     <xsd:import namespace="f76aa77c-8923-4724-9a6d-d588cc513697"/>
@@ -31861,10 +31841,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f76aa77c-8923-4724-9a6d-d588cc513697">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="89c54d5b-05ac-45d5-9242-aabb385cc5ad" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2885D72-BA50-450C-BD4C-761032353625}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DD8DB1C-B818-4A72-BFFB-70B7361B4E7B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
+    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31881,20 +31892,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DD8DB1C-B818-4A72-BFFB-70B7361B4E7B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2885D72-BA50-450C-BD4C-761032353625}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f76aa77c-8923-4724-9a6d-d588cc513697"/>
-    <ds:schemaRef ds:uri="89c54d5b-05ac-45d5-9242-aabb385cc5ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>